--- a/backend/data/financials_by_company/09D.F.xlsx
+++ b/backend/data/financials_by_company/09D.F.xlsx
@@ -3373,7 +3373,7 @@
         <v>-1289214</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
         <v>-2.681</v>
@@ -3557,7 +3557,7 @@
         <v>-50</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
         <v>-0.000109999964</v>
